--- a/Buoi9/data_slr.xlsx
+++ b/Buoi9/data_slr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tranthithanhthao/Documents/HK1(24-25)/LT PTDL1/Introduction_AI_DataAnalytics/Buoi9/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA303F3-C780-A644-A37C-6CC56FAE7B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B47816-9C44-E944-A8BE-43EC3C889B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>TimeAds</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>0.67</t>
+  </si>
+  <si>
+    <t>0.256</t>
   </si>
 </sst>
 </file>
@@ -583,6 +586,9 @@
       <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
